--- a/Config/Excel/property.xlsx
+++ b/Config/Excel/property.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>暴击伤害</t>
+  </si>
+  <si>
+    <t>命中率</t>
+  </si>
+  <si>
+    <t>闪避率</t>
   </si>
 </sst>
 </file>
@@ -1098,10 +1104,16 @@
       <c r="A12" s="1">
         <v>8</v>
       </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
         <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2">
